--- a/StructureDefinition-openimis-group.xlsx
+++ b/StructureDefinition-openimis-group.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-26T15:39:34+00:00</t>
+    <t>2025-09-08T11:14:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -10384,7 +10384,7 @@
         <v>78</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>22</v>
@@ -10828,7 +10828,7 @@
         <v>78</v>
       </c>
       <c r="G82" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="H82" t="s" s="2">
         <v>22</v>
@@ -10939,7 +10939,7 @@
         <v>78</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H83" t="s" s="2">
         <v>22</v>
@@ -12384,7 +12384,7 @@
         <v>78</v>
       </c>
       <c r="G96" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="H96" t="s" s="2">
         <v>22</v>
@@ -12497,7 +12497,7 @@
         <v>78</v>
       </c>
       <c r="G97" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="H97" t="s" s="2">
         <v>22</v>

--- a/StructureDefinition-openimis-group.xlsx
+++ b/StructureDefinition-openimis-group.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-08T11:14:40+00:00</t>
+    <t>2025-09-08T11:37:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-openimis-group.xlsx
+++ b/StructureDefinition-openimis-group.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-08T11:37:47+00:00</t>
+    <t>2025-09-08T11:49:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
